--- a/StructureDefinition-age-at-onset-observation-profile.xlsx
+++ b/StructureDefinition-age-at-onset-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-10-30T10:04:33+00:00</t>
+    <t>2026-02-09T10:35:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-age-at-onset-observation-profile.xlsx
+++ b/StructureDefinition-age-at-onset-observation-profile.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2371" uniqueCount="495">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-09T10:35:12+00:00</t>
+    <t>2026-10-27T13:25:43+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1334,6 +1334,10 @@
   <si>
     <t xml:space="preserve">obs-3
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
   </si>
   <si>
     <t>value:IVL_PQ.low</t>
@@ -7233,7 +7237,7 @@
         <v>415</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="AK44" t="s" s="2">
         <v>20</v>
@@ -7248,7 +7252,7 @@
         <v>406</v>
       </c>
       <c r="AO44" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AP44" t="s" s="2">
         <v>20</v>
@@ -7256,10 +7260,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7285,10 +7289,10 @@
         <v>412</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -7339,7 +7343,7 @@
         <v>20</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>80</v>
@@ -7351,7 +7355,7 @@
         <v>415</v>
       </c>
       <c r="AJ45" t="s" s="2">
-        <v>105</v>
+        <v>416</v>
       </c>
       <c r="AK45" t="s" s="2">
         <v>20</v>
@@ -7366,7 +7370,7 @@
         <v>406</v>
       </c>
       <c r="AO45" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AP45" t="s" s="2">
         <v>20</v>
@@ -7374,10 +7378,10 @@
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7403,10 +7407,10 @@
         <v>234</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -7436,10 +7440,10 @@
         <v>331</v>
       </c>
       <c r="Y46" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z46" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA46" t="s" s="2">
         <v>20</v>
@@ -7457,7 +7461,7 @@
         <v>20</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>80</v>
@@ -7484,7 +7488,7 @@
         <v>406</v>
       </c>
       <c r="AO46" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AP46" t="s" s="2">
         <v>20</v>
@@ -7492,10 +7496,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7521,16 +7525,16 @@
         <v>234</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>20</v>
@@ -7558,10 +7562,10 @@
         <v>239</v>
       </c>
       <c r="Y47" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="Z47" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AA47" t="s" s="2">
         <v>20</v>
@@ -7579,7 +7583,7 @@
         <v>20</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>80</v>
@@ -7600,10 +7604,10 @@
         <v>20</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN47" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO47" t="s" s="2">
         <v>346</v>
@@ -7614,10 +7618,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7643,16 +7647,16 @@
         <v>234</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>20</v>
@@ -7680,10 +7684,10 @@
         <v>251</v>
       </c>
       <c r="Y48" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="Z48" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AA48" t="s" s="2">
         <v>20</v>
@@ -7701,7 +7705,7 @@
         <v>20</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>80</v>
@@ -7722,10 +7726,10 @@
         <v>20</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AN48" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AO48" t="s" s="2">
         <v>346</v>
@@ -7736,10 +7740,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7762,17 +7766,17 @@
         <v>20</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>20</v>
@@ -7821,7 +7825,7 @@
         <v>20</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>80</v>
@@ -7848,7 +7852,7 @@
         <v>20</v>
       </c>
       <c r="AO49" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AP49" t="s" s="2">
         <v>20</v>
@@ -7856,10 +7860,10 @@
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7882,13 +7886,13 @@
         <v>20</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" s="2"/>
@@ -7939,7 +7943,7 @@
         <v>20</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>80</v>
@@ -7966,7 +7970,7 @@
         <v>406</v>
       </c>
       <c r="AO50" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AP50" t="s" s="2">
         <v>20</v>
@@ -7974,10 +7978,10 @@
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8000,16 +8004,16 @@
         <v>94</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N51" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O51" s="2"/>
       <c r="P51" t="s" s="2">
@@ -8059,7 +8063,7 @@
         <v>20</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>80</v>
@@ -8083,7 +8087,7 @@
         <v>20</v>
       </c>
       <c r="AN51" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO51" t="s" s="2">
         <v>200</v>
@@ -8094,10 +8098,10 @@
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8120,16 +8124,16 @@
         <v>94</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="O52" s="2"/>
       <c r="P52" t="s" s="2">
@@ -8179,7 +8183,7 @@
         <v>20</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>80</v>
@@ -8203,10 +8207,10 @@
         <v>20</v>
       </c>
       <c r="AN52" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="AO52" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="AP52" t="s" s="2">
         <v>20</v>
@@ -8214,10 +8218,10 @@
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8243,16 +8247,16 @@
         <v>178</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>20</v>
@@ -8301,7 +8305,7 @@
         <v>20</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>80</v>
@@ -8325,10 +8329,10 @@
         <v>20</v>
       </c>
       <c r="AN53" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AO53" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AP53" t="s" s="2">
         <v>20</v>
@@ -8336,10 +8340,10 @@
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8454,10 +8458,10 @@
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8574,10 +8578,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8696,10 +8700,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8725,13 +8729,13 @@
         <v>234</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O57" t="s" s="2">
         <v>249</v>
@@ -8783,7 +8787,7 @@
         <v>20</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>93</v>
@@ -8804,7 +8808,7 @@
         <v>256</v>
       </c>
       <c r="AM57" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AN57" t="s" s="2">
         <v>258</v>
@@ -8818,10 +8822,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8844,16 +8848,16 @@
         <v>94</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M58" t="s" s="2">
         <v>318</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="O58" t="s" s="2">
         <v>320</v>
@@ -8905,7 +8909,7 @@
         <v>20</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -8926,7 +8930,7 @@
         <v>20</v>
       </c>
       <c r="AM58" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="AN58" t="s" s="2">
         <v>323</v>
@@ -8940,10 +8944,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8969,13 +8973,13 @@
         <v>234</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="O59" t="s" s="2">
         <v>330</v>
@@ -9027,7 +9031,7 @@
         <v>20</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9062,10 +9066,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9149,7 +9153,7 @@
         <v>20</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9184,10 +9188,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9213,10 +9217,10 @@
         <v>82</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>403</v>
@@ -9271,7 +9275,7 @@
         <v>20</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>

--- a/StructureDefinition-age-at-onset-observation-profile.xlsx
+++ b/StructureDefinition-age-at-onset-observation-profile.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-27T13:25:43+00:00</t>
+    <t>2026-10-27T13:28:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
